--- a/excel/铅.xlsx
+++ b/excel/铅.xlsx
@@ -1060,98 +1060,64 @@
           <t>Tara（铅锌）</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D6" t="n">
+        <v>0.3406</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.3398</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.0215</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.7019</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.0861</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.0861</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.1891</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.1861</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.2129</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.1426</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.7307</v>
       </c>
       <c r="S6">
         <f>IF(AND(ISNUMBER(R6),ISNUMBER(M6),M6&lt;&gt;0),(R6-M6)/M6,"-")</f>
         <v/>
       </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T6" t="n">
+        <v>0.1845</v>
       </c>
       <c r="U6">
         <f>IF(AND(ISNUMBER(T6),ISNUMBER(N6),N6&lt;&gt;0),(T6-N6)/N6,"-")</f>
         <v/>
       </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="V6" t="n">
+        <v>0.2015</v>
       </c>
       <c r="W6">
         <f>IF(AND(ISNUMBER(V6),ISNUMBER(O6),O6&lt;&gt;0),(V6-O6)/O6,"-")</f>
@@ -1159,7 +1125,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>铅精矿含铅量</t>
+          <t>铅精矿含铅量；来源：Boliden官方季报(2026-08-18核查)；2023-07停产→2024Q4复产</t>
         </is>
       </c>
     </row>
@@ -1179,98 +1145,64 @@
           <t>Garpenberg（铅锌）</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D7" t="n">
+        <v>0.8964</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.9417</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.8764</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.8704</v>
+      </c>
+      <c r="H7" t="n">
+        <v>3.5849</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1.0856</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.9197</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1.1203</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.9183</v>
+      </c>
+      <c r="M7" t="n">
+        <v>4.0439</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.9164</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.9227</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.0728</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.9573</v>
+      </c>
+      <c r="R7" t="n">
+        <v>3.8692</v>
       </c>
       <c r="S7">
         <f>IF(AND(ISNUMBER(R7),ISNUMBER(M7),M7&lt;&gt;0),(R7-M7)/M7,"-")</f>
         <v/>
       </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T7" t="n">
+        <v>0.7815</v>
       </c>
       <c r="U7">
         <f>IF(AND(ISNUMBER(T7),ISNUMBER(N7),N7&lt;&gt;0),(T7-N7)/N7,"-")</f>
         <v/>
       </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="V7" t="n">
+        <v>0.0793</v>
       </c>
       <c r="W7">
         <f>IF(AND(ISNUMBER(V7),ISNUMBER(O7),O7&lt;&gt;0),(V7-O7)/O7,"-")</f>
@@ -1278,7 +1210,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>铅精矿含铅量</t>
+          <t>铅精矿含铅量；来源：Boliden官方季报(2026-08-18核查)；2026-03岩爆停产,26Q2仅793t环比-90%</t>
         </is>
       </c>
     </row>
@@ -1536,98 +1468,64 @@
           <t>Rosebery（铅锌）</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D10" t="n">
+        <v>0.3431</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.5206</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.4713</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.5797</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.9147</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.5202</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.5768</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.4285</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.5624</v>
+      </c>
+      <c r="M10" t="n">
+        <v>2.0879</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.3712</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.4635</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0.4047</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.5548</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.7942</v>
       </c>
       <c r="S10">
         <f>IF(AND(ISNUMBER(R10),ISNUMBER(M10),M10&lt;&gt;0),(R10-M10)/M10,"-")</f>
         <v/>
       </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T10" t="n">
+        <v>0.3756</v>
       </c>
       <c r="U10">
         <f>IF(AND(ISNUMBER(T10),ISNUMBER(N10),N10&lt;&gt;0),(T10-N10)/N10,"-")</f>
         <v/>
       </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="V10" t="n">
+        <v>0.4093</v>
       </c>
       <c r="W10">
         <f>IF(AND(ISNUMBER(V10),ISNUMBER(O10),O10&lt;&gt;0),(V10-O10)/O10,"-")</f>
@@ -1635,7 +1533,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>铅精矿含铅量；100% 矿山口径</t>
+          <t>铅精矿含铅量；100% 矿山口径；来源：MMG港交所季度生产报告(2026-08-18核查)；100%矿山口径</t>
         </is>
       </c>
     </row>
@@ -1655,98 +1553,64 @@
           <t>Dugald River（锌为主）</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D11" t="n">
+        <v>0.2261</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.4279</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.6441</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.6927</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.9907</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.6181</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.4618</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.4295</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.5687</v>
+      </c>
+      <c r="M11" t="n">
+        <v>2.0781</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.5004999999999999</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.3801</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0.5778</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.7082000000000001</v>
+      </c>
+      <c r="R11" t="n">
+        <v>2.1666</v>
       </c>
       <c r="S11">
         <f>IF(AND(ISNUMBER(R11),ISNUMBER(M11),M11&lt;&gt;0),(R11-M11)/M11,"-")</f>
         <v/>
       </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T11" t="n">
+        <v>0.5058</v>
       </c>
       <c r="U11">
         <f>IF(AND(ISNUMBER(T11),ISNUMBER(N11),N11&lt;&gt;0),(T11-N11)/N11,"-")</f>
         <v/>
       </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="V11" t="n">
+        <v>0.5799</v>
       </c>
       <c r="W11">
         <f>IF(AND(ISNUMBER(V11),ISNUMBER(O11),O11&lt;&gt;0),(V11-O11)/O11,"-")</f>
@@ -1754,7 +1618,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>铅精矿含铅量（伴生少量）</t>
+          <t>铅精矿含铅量（伴生少量）；来源：MMG港交所季度生产报告(2026-08-18核查)；2025创纪录</t>
         </is>
       </c>
     </row>
@@ -1774,98 +1638,64 @@
           <t>Cannington（铅银矿）</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D12" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="E12" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="G12" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="H12" t="n">
+        <v>10.81</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="L12" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="M12" t="n">
+        <v>10.32</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="O12" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R12" t="n">
+        <v>8.51</v>
       </c>
       <c r="S12">
         <f>IF(AND(ISNUMBER(R12),ISNUMBER(M12),M12&lt;&gt;0),(R12-M12)/M12,"-")</f>
         <v/>
       </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T12" t="n">
+        <v>1.78</v>
       </c>
       <c r="U12">
         <f>IF(AND(ISNUMBER(T12),ISNUMBER(N12),N12&lt;&gt;0),(T12-N12)/N12,"-")</f>
         <v/>
       </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="V12" t="n">
+        <v>2.28</v>
       </c>
       <c r="W12">
         <f>IF(AND(ISNUMBER(V12),ISNUMBER(O12),O12&lt;&gt;0),(V12-O12)/O12,"-")</f>
@@ -1873,7 +1703,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>铅精矿含铅量；财年止6月，权益口径</t>
+          <t>铅精矿含铅量；财年止6月，权益口径；来源：South32季报SENS(2026-08-18核查)；应付铅payable权益口径,财年止6月已映射自然季,年度为自然年加总</t>
         </is>
       </c>
     </row>
@@ -1913,10 +1743,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H13" t="n">
+        <v>22.3</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1938,10 +1766,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M13" t="n">
+        <v>22.41</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -1963,10 +1789,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="R13" t="n">
+        <v>23.16</v>
       </c>
       <c r="S13">
         <f>IF(AND(ISNUMBER(R13),ISNUMBER(M13),M13&lt;&gt;0),(R13-M13)/M13,"-")</f>
@@ -1992,7 +1816,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>铅精矿含铅量；财年止3月</t>
+          <t>铅精矿含铅量；财年止3月；来源：HZL年报KPI(2026-08-18核查)；矿产铅财年口径(止3月),季度不拆分披露</t>
         </is>
       </c>
     </row>
@@ -2012,98 +1836,64 @@
           <t>多矿（铅锌）</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D14" t="n">
+        <v>1.904</v>
+      </c>
+      <c r="E14" t="n">
+        <v>2.103</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2.206</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="H14" t="n">
+        <v>8.542999999999999</v>
+      </c>
+      <c r="I14" t="n">
+        <v>2.143</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2.345</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2.349</v>
+      </c>
+      <c r="L14" t="n">
+        <v>2.128</v>
+      </c>
+      <c r="M14" t="n">
+        <v>8.965</v>
+      </c>
+      <c r="N14" t="n">
+        <v>1.948</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1.992</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2.357</v>
+      </c>
+      <c r="R14" t="n">
+        <v>8.516</v>
       </c>
       <c r="S14">
         <f>IF(AND(ISNUMBER(R14),ISNUMBER(M14),M14&lt;&gt;0),(R14-M14)/M14,"-")</f>
         <v/>
       </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T14" t="n">
+        <v>2.35</v>
       </c>
       <c r="U14">
         <f>IF(AND(ISNUMBER(T14),ISNUMBER(N14),N14&lt;&gt;0),(T14-N14)/N14,"-")</f>
         <v/>
       </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="V14" t="n">
+        <v>2.563</v>
       </c>
       <c r="W14">
         <f>IF(AND(ISNUMBER(V14),ISNUMBER(O14),O14&lt;&gt;0),(V14-O14)/O14,"-")</f>
@@ -2111,7 +1901,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>铅精矿含铅量</t>
+          <t>铅精矿含铅量；来源：Peñoles官网季报PDF(2026-08-18核查)；合并口径含Fresnillo 100%+Juanicipio,与Fresnillo行严禁相加</t>
         </is>
       </c>
     </row>
@@ -2131,98 +1921,64 @@
           <t>多矿（铅锌）</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D15" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="H15" t="n">
+        <v>6.08</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="M15" t="n">
+        <v>5.46</v>
+      </c>
+      <c r="N15" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6.37</v>
       </c>
       <c r="S15">
         <f>IF(AND(ISNUMBER(R15),ISNUMBER(M15),M15&lt;&gt;0),(R15-M15)/M15,"-")</f>
         <v/>
       </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T15" t="n">
+        <v>1.28</v>
       </c>
       <c r="U15">
         <f>IF(AND(ISNUMBER(T15),ISNUMBER(N15),N15&lt;&gt;0),(T15-N15)/N15,"-")</f>
         <v/>
       </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="V15" t="n">
+        <v>1.48</v>
       </c>
       <c r="W15">
         <f>IF(AND(ISNUMBER(V15),ISNUMBER(O15),O15&lt;&gt;0),(V15-O15)/O15,"-")</f>
@@ -2230,7 +1986,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>铅精矿含铅量</t>
+          <t>铅精矿含铅量；来源：Volcan BVL/SMV季报(2026-08-18核查)；2026起口径含附加金属,与此前不完全可比;2026指引6.5-7.5万吨</t>
         </is>
       </c>
     </row>
@@ -2250,98 +2006,64 @@
           <t>Fresnillo/Saucito（铅银）</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D16" t="n">
+        <v>1.337</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1.399</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1.458</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="H16" t="n">
+        <v>5.783</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.492</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1.691</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1.771</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1.686</v>
+      </c>
+      <c r="M16" t="n">
+        <v>6.64</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1.503</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1.515</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1.536</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1.654</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6.208</v>
       </c>
       <c r="S16">
         <f>IF(AND(ISNUMBER(R16),ISNUMBER(M16),M16&lt;&gt;0),(R16-M16)/M16,"-")</f>
         <v/>
       </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T16" t="n">
+        <v>1.539</v>
       </c>
       <c r="U16">
         <f>IF(AND(ISNUMBER(T16),ISNUMBER(N16),N16&lt;&gt;0),(T16-N16)/N16,"-")</f>
         <v/>
       </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="V16" t="n">
+        <v>1.744</v>
       </c>
       <c r="W16">
         <f>IF(AND(ISNUMBER(V16),ISNUMBER(O16),O16&lt;&gt;0),(V16-O16)/O16,"-")</f>
@@ -2349,7 +2071,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>铅精矿含铅量</t>
+          <t>铅精矿含铅量；来源：Fresnillo LSE RNS全文(2026-08-18核查)；100%合并口径;2026指引6.5-7.0万吨</t>
         </is>
       </c>
     </row>
@@ -2369,98 +2091,64 @@
           <t>Antamina（33.75%权益）</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D17" t="n">
+        <v>0.0169</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.0146</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.009599999999999999</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.0105</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.0516</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.0131</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.0021</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.0148</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.0234</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.1829</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0.07539999999999999</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.0091</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.2908</v>
       </c>
       <c r="S17">
         <f>IF(AND(ISNUMBER(R17),ISNUMBER(M17),M17&lt;&gt;0),(R17-M17)/M17,"-")</f>
         <v/>
       </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T17" t="n">
+        <v>0.0209</v>
       </c>
       <c r="U17">
         <f>IF(AND(ISNUMBER(T17),ISNUMBER(N17),N17&lt;&gt;0),(T17-N17)/N17,"-")</f>
         <v/>
       </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="V17" t="n">
+        <v>0.0225</v>
       </c>
       <c r="W17">
         <f>IF(AND(ISNUMBER(V17),ISNUMBER(O17),O17&lt;&gt;0),(V17-O17)/O17,"-")</f>
@@ -2468,7 +2156,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>铅精矿含铅量；权益口径，财年止6月</t>
+          <t>铅精矿含铅量；权益口径，财年止6月；来源：BHP 6-K运营报告(2026-08-18核查)；应付铅33.75%权益,量级极小,年度为自然年加总</t>
         </is>
       </c>
     </row>
@@ -2488,98 +2176,64 @@
           <t>Peñasquito（铅锌副产）</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D18" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="E18" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="H18" t="n">
+        <v>5.13</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="L18" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="M18" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="N18" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="O18" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R18" t="n">
+        <v>9.800000000000001</v>
       </c>
       <c r="S18">
         <f>IF(AND(ISNUMBER(R18),ISNUMBER(M18),M18&lt;&gt;0),(R18-M18)/M18,"-")</f>
         <v/>
       </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T18" t="n">
+        <v>2.7</v>
       </c>
       <c r="U18">
         <f>IF(AND(ISNUMBER(T18),ISNUMBER(N18),N18&lt;&gt;0),(T18-N18)/N18,"-")</f>
         <v/>
       </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="V18" t="n">
+        <v>1.8</v>
       </c>
       <c r="W18">
         <f>IF(AND(ISNUMBER(V18),ISNUMBER(O18),O18&lt;&gt;0),(V18-O18)/O18,"-")</f>
@@ -2587,7 +2241,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>铅精矿含铅量</t>
+          <t>铅精矿含铅量；来源：Newmont 10-Q/10-K/8-K(2026-08-18核查)；2023Q3罢工整季停产=0;2026指引9.0万吨</t>
         </is>
       </c>
     </row>
@@ -2627,10 +2281,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H19" t="n">
+        <v>1.87</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -2652,10 +2304,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M19" t="n">
+        <v>2.11</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
@@ -2677,10 +2327,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="R19" t="n">
+        <v>2.49</v>
       </c>
       <c r="S19">
         <f>IF(AND(ISNUMBER(R19),ISNUMBER(M19),M19&lt;&gt;0),(R19-M19)/M19,"-")</f>
@@ -2706,7 +2354,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>铅精矿含铅量</t>
+          <t>铅精矿含铅量；来源：SCCO 10-K年报IMMSA表(2026-08-18核查)；季度不披露铅,仅年度</t>
         </is>
       </c>
     </row>
@@ -4262,98 +3910,64 @@
           <t>Torreon 精炼铅</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D6" t="n">
+        <v>2.467</v>
+      </c>
+      <c r="E6" t="n">
+        <v>3.037</v>
+      </c>
+      <c r="F6" t="n">
+        <v>3.147</v>
+      </c>
+      <c r="G6" t="n">
+        <v>3.329</v>
+      </c>
+      <c r="H6" t="n">
+        <v>11.979</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.516</v>
+      </c>
+      <c r="J6" t="n">
+        <v>3.017</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2.728</v>
+      </c>
+      <c r="L6" t="n">
+        <v>3.234</v>
+      </c>
+      <c r="M6" t="n">
+        <v>11.493</v>
+      </c>
+      <c r="N6" t="n">
+        <v>3.079</v>
+      </c>
+      <c r="O6" t="n">
+        <v>2.646</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1.988</v>
+      </c>
+      <c r="R6" t="n">
+        <v>10.512</v>
       </c>
       <c r="S6">
         <f>IF(AND(ISNUMBER(R6),ISNUMBER(M6),M6&lt;&gt;0),(R6-M6)/M6,"-")</f>
         <v/>
       </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T6" t="n">
+        <v>2.34</v>
       </c>
       <c r="U6">
         <f>IF(AND(ISNUMBER(T6),ISNUMBER(N6),N6&lt;&gt;0),(T6-N6)/N6,"-")</f>
         <v/>
       </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="V6" t="n">
+        <v>2.569</v>
       </c>
       <c r="W6">
         <f>IF(AND(ISNUMBER(V6),ISNUMBER(O6),O6&lt;&gt;0),(V6-O6)/O6,"-")</f>
@@ -4361,7 +3975,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>精炼铅产量</t>
+          <t>精炼铅产量；来源：Peñoles官网季报PDF(2026-08-18核查)；2025Q4年度检修移至Q4</t>
         </is>
       </c>
     </row>
@@ -4406,73 +4020,49 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I7" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="J7" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="L7" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="M7" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="N7" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="O7" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="P7" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="R7" t="n">
+        <v>20.5</v>
       </c>
       <c r="S7">
         <f>IF(AND(ISNUMBER(R7),ISNUMBER(M7),M7&lt;&gt;0),(R7-M7)/M7,"-")</f>
         <v/>
       </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T7" t="n">
+        <v>5.5</v>
       </c>
       <c r="U7">
         <f>IF(AND(ISNUMBER(T7),ISNUMBER(N7),N7&lt;&gt;0),(T7-N7)/N7,"-")</f>
         <v/>
       </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="V7" t="n">
+        <v>4.7</v>
       </c>
       <c r="W7">
         <f>IF(AND(ISNUMBER(V7),ISNUMBER(O7),O7&lt;&gt;0),(V7-O7)/O7,"-")</f>
@@ -4480,7 +4070,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>精炼铅产量；财年止3月</t>
+          <t>精炼铅产量；财年止3月；来源：Vedanta/HZL季度公告(2026-08-18核查)；排除自用口径;2024Q3为同比反推推算值,2024总计含该推算;FY26(止2026-03)=19.7同比-13%</t>
         </is>
       </c>
     </row>
@@ -5284,7 +4874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5343,6 +4933,23 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>回填产量数据：铅精矿 12 行（Boliden两矿/MMG两矿/South32 Cannington/Vedanta年度/Peñoles/Volcan/Fresnillo/BHP Antamina/Newmont/SCCO年度）+ 精炼铅 2 行（Peñoles Torreon、HZL），2023Q1-2026Q2</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>各公司官方季报/年报（2026-08-18 核查底稿 _pb_fill.json）</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
